--- a/tame_output/ON/bt/strategyON_20230823.xlsx
+++ b/tame_output/ON/bt/strategyON_20230823.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,16 +758,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,16 +911,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.5%</t>
+          <t>454.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>134.1%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>128.5%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1697"/>
+  <dimension ref="A1:G1698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40541,7 +40541,7 @@
         <v>45159</v>
       </c>
       <c r="B1697" t="n">
-        <v>2.767457125596384</v>
+        <v>2.768404591087867</v>
       </c>
       <c r="C1697" t="n">
         <v>2.896213149298758</v>
@@ -40557,6 +40557,29 @@
       </c>
       <c r="G1697" t="n">
         <v>4.20441384951242</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="2" t="n">
+        <v>45160</v>
+      </c>
+      <c r="B1698" t="n">
+        <v>2.766742018168002</v>
+      </c>
+      <c r="C1698" t="n">
+        <v>2.895302714668627</v>
+      </c>
+      <c r="D1698" t="n">
+        <v>1.546945776488526</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>3.51372460095029</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>2.167322911473179</v>
+      </c>
+      <c r="G1698" t="n">
+        <v>4.195696461552536</v>
       </c>
     </row>
   </sheetData>
